--- a/CRM_Global_Locators.xlsx
+++ b/CRM_Global_Locators.xlsx
@@ -8,13 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Universal_Framework_For_Web_And_Mobile_Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AAB183-33FF-45F9-BA33-C6E5F718047D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BECFE8-65C4-4070-8D00-BE1629FA0C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="crm_login_page" sheetId="43" r:id="rId1"/>
-    <sheet name="crm_dashboard" sheetId="44" r:id="rId2"/>
+    <sheet name="crm_side_bar" sheetId="57" r:id="rId2"/>
+    <sheet name="crm_dashboard" sheetId="44" r:id="rId3"/>
+    <sheet name="crm_notifications" sheetId="45" r:id="rId4"/>
+    <sheet name="crm_leads" sheetId="46" r:id="rId5"/>
+    <sheet name="crm_qualified" sheetId="47" r:id="rId6"/>
+    <sheet name="crm_opportunities" sheetId="48" r:id="rId7"/>
+    <sheet name="crm_quotations" sheetId="49" r:id="rId8"/>
+    <sheet name="crm_deals" sheetId="50" r:id="rId9"/>
+    <sheet name="crm_customers" sheetId="51" r:id="rId10"/>
+    <sheet name="crm_followups" sheetId="52" r:id="rId11"/>
+    <sheet name="crm_calender" sheetId="53" r:id="rId12"/>
+    <sheet name="crm_email_threads" sheetId="54" r:id="rId13"/>
+    <sheet name="crm_web_scraping" sheetId="55" r:id="rId14"/>
+    <sheet name="crm_blog" sheetId="56" r:id="rId15"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,20 +39,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="130">
   <si>
     <t>locators</t>
   </si>
   <si>
-    <t># =========================================================================</t>
-  </si>
-  <si>
     <t># CRM LOGIN PAGE LOCATORS REPOSITORY</t>
   </si>
   <si>
-    <t># CRM LOGIN FORM ELEMENTS</t>
-  </si>
-  <si>
     <t>crm.login_page.email_input_field=//input[@id='login_email']</t>
   </si>
   <si>
@@ -52,17 +59,591 @@
     <t># CRM DASHBOARD LOCATORS REPOSITORY</t>
   </si>
   <si>
-    <t># DASHBOARD SIDE BAR ELEMENTS</t>
-  </si>
-  <si>
-    <t>crm.dashboard.dashboard_siderbar_menu=//span[normalize-space()='Dashboard']</t>
+    <t>crm.dashboard.dashboard_heading=//div[@class='page-h1' and text()='Dashboard']</t>
+  </si>
+  <si>
+    <t># CRM SIDEBAR LOCATORS REPOSITORY</t>
+  </si>
+  <si>
+    <t>crm.side_bar.dashboard_menu=//span[normalize-space()='Dashboard']</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRM LOGIN FORM ELEMENTS</t>
+    </r>
+  </si>
+  <si>
+    <t># =====================================</t>
+  </si>
+  <si>
+    <t># =================================</t>
+  </si>
+  <si>
+    <t>crm.side_bar.notifications_menu=//span[normalize-space()='Notifications']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.leads_menu=//span[normalize-space()='Leads']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.qualified_menu=//span[normalize-space()='Qualified']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.opportunities_menu=//span[normalize-space()='Opportunities']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.quotations_menu=//span[normalize-space()='Quotations']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.deals_menu=//span[normalize-space()='Deals']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.customers_menu=//span[normalize-space()='Customers']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.calendar_menu=//span[normalize-space()='Calendar']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.followups_menu=//span[normalize-space()='Follow-Ups']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.email_threads_menu=//span[normalize-space()='Email Threads']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.web_scraping_menu=//span[normalize-space()='Web Scraping']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.blog_menu=//span[normalize-space()='Blog']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.administrator_menu=//b[normalize-space()='Administrator']</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRM LOGIN FORM LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRM SIDE BAR LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <t>crm.side_bar.administrator_menu.switch_to_desk=//span[normalize-space()='Switch to Desk']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.administrator_menu.desk.admin_icon=//div[@title='Administrator']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.administrator_menu.desk_admin.logout=//span[normalize-space()='Logout']</t>
+  </si>
+  <si>
+    <r>
+      <t>#</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRM SIDE BAR ADMINISTRATOR SUB MENU LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRM SIDE BAR  CRM MODULE SUB MENU LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <t>crm.side_bar.crm_module_menu=//span[@class='ms-label' and text()='CRM Module']</t>
+  </si>
+  <si>
+    <t>crm.side_bar.crm_module_menu.crm_menu=//span[normalize-space()='CRM']</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DASHBOARD HEADING LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <t># CRM NOTIFICATIONS LOCATORS REPOSITORY</t>
+  </si>
+  <si>
+    <t># ========================================</t>
+  </si>
+  <si>
+    <t># CRM LEADS LOCATORS REPOSITORY</t>
+  </si>
+  <si>
+    <t># ================================</t>
+  </si>
+  <si>
+    <t># CRM QUALIFIED LOCATORS REPOSITORY</t>
+  </si>
+  <si>
+    <t># CRM OPPORTUNITIES LOCATORS REPOSITORY</t>
+  </si>
+  <si>
+    <t># =========================================</t>
+  </si>
+  <si>
+    <t># =======================================</t>
+  </si>
+  <si>
+    <t># CRM QUOTATIONS LOCATORS REPOSITORY</t>
+  </si>
+  <si>
+    <t># ======================================</t>
+  </si>
+  <si>
+    <t># CRM DEALS LOCATORS REPOSITORY</t>
+  </si>
+  <si>
+    <t># CRM CUSTOMERS REPOSITORY</t>
+  </si>
+  <si>
+    <t># ============================</t>
+  </si>
+  <si>
+    <t># CRM FOLLOWUPS LOCATORS REPOSITORY</t>
+  </si>
+  <si>
+    <t># CRM CALENDER LOCATORS REPOSITORY</t>
+  </si>
+  <si>
+    <t># ====================================</t>
+  </si>
+  <si>
+    <t># CRM EMAIL THREADS REPOSITORY</t>
+  </si>
+  <si>
+    <t># ===============================</t>
+  </si>
+  <si>
+    <t># CRM WEB SCRAPING LOCATORS REPOSITORY</t>
+  </si>
+  <si>
+    <r>
+      <t>#</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CRM LOGIN FORM ELEMENTS</t>
+    </r>
+  </si>
+  <si>
+    <t># CRM BLOG LOCATORS REPOSITORY</t>
+  </si>
+  <si>
+    <t>crm.dashboard.stat_cards.new_leads=//span[normalize-space()='New Leads']</t>
+  </si>
+  <si>
+    <t>crm.dashboard.stat_cards.Quailfied_leads=//span[normalize-space()='Qualified Leads']</t>
+  </si>
+  <si>
+    <t>crm.dashboard.stat_cards.opportunities=//span[normalize-space()='Opportunities']</t>
+  </si>
+  <si>
+    <t>crm.dashboard.stat_cards.quaotations=//span[normalize-space()='Quotations']</t>
+  </si>
+  <si>
+    <t>crm.dashboard.stat_cards.won_deals=//span[normalize-space()='Won Deals']</t>
+  </si>
+  <si>
+    <t>crm.dashboard.stat_cards.revenue=//span[normalize-space()='Revenue']</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DASHBOARD TODAY STAT CARDS LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <t>crm.dashboard.today_stat_cards.new_leads=//button[@title='View New Leads · raised today']//span[@class='ac-line']</t>
+  </si>
+  <si>
+    <t>crm.dashboard.today_stat_cards.follow_ups=//button[@title='View Follow-Ups · due today']//span[@class='ac-line']</t>
+  </si>
+  <si>
+    <t>crm.dashboard.today_stat_cards.meetings=//button[@title='View Meetings · today']//span[@class='ac-line']</t>
+  </si>
+  <si>
+    <t>crm.dashboard.today_stat_cards.overdue=//button[@title='View Overdue · past due, all of it']//span[@class='ac-line']</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DASHBOARD SELECTED_STAT CARDS LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <t>crm.notifications.notifications_heading=//div[@class='page-h1' and text()='Notifications']</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRM NOTIFICATIONS HEADING ELEMENTS</t>
+    </r>
+  </si>
+  <si>
+    <t>crm.leads.leads_heading=//div[@class='page-h1' and text()='Leads']</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRM LEADs HEADING LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRM ADD  NEW LEADS LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <t>crm.leads.new_leads.add_button=//button[contains(@class, 'btn-primary') and contains(., 'New Lead')]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRM CREATE  NEW LEADS FORM LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.lead_title_field=//input[@placeholder='e.g. CRM rollout enquiry']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.job_title_field=//input[@placeholder='e.g. Procurement Head']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.first_name_field=//input[@placeholder='e.g. Rahul']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.last_name_field=//input[@placeholder='e.g. Sharma']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.email_field=//input[@placeholder='name@company.com']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.phone_field=//label[text()='Phone']/following-sibling::input</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.alternate_phone_field=//label[text()='Alternate Phone Number']/following-sibling::input</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.whatsapp_field=//label[text()='WhatsApp Number']/following-sibling::input</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.gender_option_male=//span[normalize-space()='Male']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.website_url_field=//input[@placeholder='https://…']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.sales_user_option=(//label[text()='Sales User']/following-sibling::div//button[@role='option'])[1]</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.gender_dropdown=//label[text()='Gender']/following-sibling::div//button</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.sales_user_dropdown=//label[text()='Sales User']/following-sibling::div//button</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.status_dropdown=//label[text()='Status']/following-sibling::div//button</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.status_option=//div[@role='listbox']//button[@role='option' and .//span[text()='New']]</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.territory_dropdown=//label[text()='Territory']/following-sibling::div//button</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.territory_option=//button[@role='option']//span[contains(text(),'India')]</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.lead_type_options=//span[normalize-space()='IOT']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.company_name_field=//input[@placeholder='Company name']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.lead_type_dropdown=//label[text()='Lead Type']/following-sibling::div//button</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.industry_dropdown=//label[text()='Industry']/following-sibling::div//button</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.industry_options=//span[normalize-space()='Accounting']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.city_field=//label[text()='City']/following-sibling::input</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.annual_revenue_field=//input[@type='number']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.source_dropdown=//label[text()='Source']/following-sibling::div//button</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.source_options=//span[normalize-space()='Advertisement']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.website_field=//input[@placeholder='EIT']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.category_field=//label[text()='Category']/following-sibling::div//button</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.category_options=//span[normalize-space()='About Us']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.request_type_dropdown=//label[text()='Request Type']/following-sibling::div//button</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.request_type_options=//span[normalize-space()='Product Enquiry']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.refrence_dropdown=//label[text()='Campaign / Reference']/following-sibling::div//button</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.refrence_options=//span[normalize-space()='airport']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.country_dropdwon=//label[text()='Country']/following-sibling::div//button</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.country_options=//span[normalize-space()='India']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.state_field=//input[@placeholder='e.g. Maharashtra']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.description_input_field=//textarea[@placeholder='Describe the lead — requirement, background, key context…']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.notes_input_field=//textarea[@placeholder='Context, requirements, next steps…']</t>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.create_lead.button=//div[@class='head-actions']//button[@class='btn btn-primary'][normalize-space()='Create Lead']</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRM CREATE  LEADS AND CANCEL LEAD BUTTON LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <t>crm.leads.add_new_leads.cancel_lead.button=//button[text()='Cancel']</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRM INDIVIDUAL LEADS OPERATION BUTTON LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <t>crm.leads.individual_leads.edit_button=//button[normalize-space()='Edit']</t>
+  </si>
+  <si>
+    <t>crm.leads.individual_leads.mark_lost_button=//button[normalize-space()='Mark Lost']</t>
+  </si>
+  <si>
+    <t>crm.leads.individual_leads.move_to_qualified_button=//button[normalize-space()='Move to Qualified']</t>
+  </si>
+  <si>
+    <t>crm.leads.individual_leads.convert_to_opportunity_button=//button[contains(normalize-space(), 'Convert to Opportunity')]</t>
+  </si>
+  <si>
+    <t>crm.leads.individual_leads.assign_users_button=//button[contains(normalize-space(), 'Assign')]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRM INDIVIDUAL LEADS SUB MENU LOCATORS</t>
+    </r>
+  </si>
+  <si>
+    <t>crm.leads.individual_leads.sub_menu_summary=//button[normalize-space()='Summary']</t>
+  </si>
+  <si>
+    <t>crm.leads.individual_leads.sub_menu_tasks=//button[contains(normalize-space(), 'Tasks')]</t>
+  </si>
+  <si>
+    <t>crm.leads.individual_leads.sub_menu_events=//button[contains(normalize-space(), 'Events')]</t>
+  </si>
+  <si>
+    <t>crm.leads.individual_leads.sub_menu_emails=//button[contains(normalize-space(), 'Emails')]</t>
+  </si>
+  <si>
+    <t>crm.leads.individual_leads.sub_menu_notes=//button[contains(normalize-space(), 'Notes')]</t>
+  </si>
+  <si>
+    <t>crm.leads.individual_leads.sub_menu_activity=//button[contains(normalize-space(), 'Activity')]</t>
+  </si>
+  <si>
+    <t>crm.leads.individual_leads.sub_menu_files=//button[contains(normalize-space(), 'Files')]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,6 +655,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -428,7 +1017,7 @@
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -440,7 +1029,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="2"/>
@@ -453,27 +1042,537 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA039114-E36B-4285-95AD-17B9EF10A293}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FBF8773-52D1-4308-B8CE-DE2ED057DC6B}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6FE4422-F902-4543-88C8-35744B3C6D39}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B9FA7D7-7789-45CA-BF31-0703C268CE16}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27D3F41-6AEE-40C5-87F3-283A9B314133}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4AC9965-2363-40C4-9425-7CB98953A3DF}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -483,7 +1582,317 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37A973E1-82BC-4D84-8C81-A8EAAD8958EB}">
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F6B71E6-2EEF-4B20-AFAB-E9260CB7D220}">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD20BD6F-00DE-4D31-9412-BDEBFD707FD3}">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -513,7 +1922,7 @@
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -525,7 +1934,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="2"/>
@@ -538,17 +1947,727 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD64E33-30C6-4280-B2A9-ECEE8E54F56F}">
+  <dimension ref="A1:I71"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{023276A3-FB4D-49C9-81CF-41C4243684B6}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08AF4FF-8064-41F8-B756-755406E5717D}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F73398-EAE0-40B6-8CFD-EBB62E995828}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CFEC505-72F2-44F1-AB77-69C8DE6A00A5}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="190" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
